--- a/chumonsho_A5.xlsx
+++ b/chumonsho_A5.xlsx
@@ -8,19 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahono\Documents\株式会社若林商店\発注書書き方マニュアル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8410C9DC-D2C8-496C-A6E1-C5219DA4057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A207D1D9-5DCD-4CDF-AC75-3E731933131E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="注文書" sheetId="1" r:id="rId1"/>
-    <sheet name="商品名一覧" sheetId="2" r:id="rId2"/>
-    <sheet name="備考一覧" sheetId="4" r:id="rId3"/>
-    <sheet name="使い方" sheetId="5" r:id="rId4"/>
-    <sheet name="日付リスト" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="業者発注票" sheetId="6" r:id="rId2"/>
+    <sheet name="注文書 (2)" sheetId="7" r:id="rId3"/>
+    <sheet name="商品名一覧" sheetId="2" r:id="rId4"/>
+    <sheet name="備考一覧" sheetId="4" r:id="rId5"/>
+    <sheet name="使い方" sheetId="5" r:id="rId6"/>
+    <sheet name="日付リスト" sheetId="3" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">注文書!$A$1:$D$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">業者発注票!$A$1:$D$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">注文書!$A$1:$E$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'注文書 (2)'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,15 +44,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="98">
   <si>
     <t>記入日</t>
   </si>
   <si>
     <t>注　文　書</t>
-  </si>
-  <si>
-    <t>（業者発注票）</t>
   </si>
   <si>
     <t>下記のとおり注文します。</t>
@@ -628,10 +629,6 @@
     <t>選択しない</t>
   </si>
   <si>
-    <t>必要であれば年月を選択</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ササミなどの本数発注は重量未記入でOKです</t>
     <rPh sb="6" eb="8">
       <t>ホンスウ</t>
@@ -645,11 +642,36 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>施設名記入</t>
+    <t>株式会社若林商店 殿</t>
+    <rPh sb="0" eb="3">
+      <t>ワカバヤシシゲル</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ドノ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>株式会社若林商店宛　FAX03-3637-8501</t>
+    <t>園長印</t>
+  </si>
+  <si>
+    <t>（保育園控え）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>（業者発注票）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>（施設名）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>レ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>単位呼称</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -657,13 +679,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="m/d\(aaa\)"/>
-    <numFmt numFmtId="177" formatCode="0.###&quot; kg&quot;"/>
-    <numFmt numFmtId="178" formatCode="yyyy&quot;年&quot;m&quot;月分&quot;"/>
-    <numFmt numFmtId="179" formatCode="General&quot; kg&quot;"/>
+    <numFmt numFmtId="177" formatCode="yyyy&quot;年&quot;m&quot;月分&quot;"/>
+    <numFmt numFmtId="178" formatCode="General&quot; kg&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -765,6 +786,21 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -780,7 +816,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -818,18 +854,231 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,14 +1103,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -892,14 +1134,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -908,14 +1161,93 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1224,7 +1556,259 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" style="8" customWidth="1"/>
+    <col min="3" max="4" width="12.90625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10">
+        <f ca="1">TODAY()</f>
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+    </row>
+    <row r="4" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+    </row>
+    <row r="5" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="C5" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" spans="1:5" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="30"/>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="30"/>
+    </row>
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="30"/>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="30"/>
+    </row>
+    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="30"/>
+    </row>
+    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="30"/>
+    </row>
+    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="30"/>
+    </row>
+    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="30"/>
+    </row>
+    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="30"/>
+    </row>
+    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="18"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="30"/>
+    </row>
+    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="30"/>
+    </row>
+    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="30"/>
+    </row>
+    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="18"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="30"/>
+    </row>
+    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="30"/>
+    </row>
+    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="30"/>
+    </row>
+    <row r="23" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+    </row>
+    <row r="24" spans="1:5" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>ISNUMBER($B$1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="11" scale="77" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{D67EA904-5FF8-4687-8A2C-124F5F44FD48}">
+          <x14:formula1>
+            <xm:f>OFFSET(日付リスト!$A$2,0,0,COUNT(日付リスト!$A$2:$A$46),1)</xm:f>
+          </x14:formula1>
+          <xm:sqref>A8:A23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{01542218-C740-4094-ADE7-4A3A6884B42B}">
+          <x14:formula1>
+            <xm:f>日付リスト!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{13D6FBBB-F314-4BEC-B11B-EA8AB336D583}">
+          <x14:formula1>
+            <xm:f>商品名一覧!$A$2:$A$53</xm:f>
+          </x14:formula1>
+          <xm:sqref>B8:C23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{F8012672-5D7E-49A8-A4B5-9FE9796B914C}">
+          <x14:formula1>
+            <xm:f>備考一覧!$A$2:$A$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>C8:C23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD386119-26EC-45CA-8345-248489C4CBB5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.26953125" style="8" customWidth="1"/>
@@ -1234,183 +1818,599 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="20" t="s">
-        <v>91</v>
+      <c r="B1" s="17" t="str">
+        <f>IF(注文書!B1="","",注文書!B1)</f>
+        <v>選択しない</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="10">
-        <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <f ca="1">IF(注文書!D1="","",注文書!D1)</f>
+        <v>46212</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="11" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="32"/>
+      <c r="A3" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="33" t="str">
+        <f>IF(注文書!C3="","",注文書!C3)</f>
+        <v/>
+      </c>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
+        <v>2</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
     </row>
     <row r="5" spans="1:4" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="C6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="23"/>
+      <c r="A7" s="18" t="str">
+        <f>IF(注文書!A8="","",注文書!A8)</f>
+        <v/>
+      </c>
+      <c r="B7" s="19" t="str">
+        <f>IF(注文書!B8="","",注文書!B8)</f>
+        <v/>
+      </c>
+      <c r="C7" s="25" t="str">
+        <f>IF(注文書!D8="","",注文書!D8)</f>
+        <v/>
+      </c>
+      <c r="D7" s="20" t="str">
+        <f>IF(注文書!C8="","",注文書!C8)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
+      <c r="A8" s="18" t="str">
+        <f>IF(注文書!A9="","",注文書!A9)</f>
+        <v/>
+      </c>
+      <c r="B8" s="21" t="str">
+        <f>IF(注文書!B9="","",注文書!B9)</f>
+        <v/>
+      </c>
+      <c r="C8" s="25" t="str">
+        <f>IF(注文書!D9="","",注文書!D9)</f>
+        <v/>
+      </c>
+      <c r="D8" s="22" t="str">
+        <f>IF(注文書!C9="","",注文書!C9)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
+      <c r="A9" s="18" t="str">
+        <f>IF(注文書!A10="","",注文書!A10)</f>
+        <v/>
+      </c>
+      <c r="B9" s="21" t="str">
+        <f>IF(注文書!B10="","",注文書!B10)</f>
+        <v/>
+      </c>
+      <c r="C9" s="25" t="str">
+        <f>IF(注文書!D10="","",注文書!D10)</f>
+        <v/>
+      </c>
+      <c r="D9" s="22" t="str">
+        <f>IF(注文書!C10="","",注文書!C10)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
+      <c r="A10" s="18" t="str">
+        <f>IF(注文書!A11="","",注文書!A11)</f>
+        <v/>
+      </c>
+      <c r="B10" s="21" t="str">
+        <f>IF(注文書!B11="","",注文書!B11)</f>
+        <v/>
+      </c>
+      <c r="C10" s="25" t="str">
+        <f>IF(注文書!D11="","",注文書!D11)</f>
+        <v/>
+      </c>
+      <c r="D10" s="22" t="str">
+        <f>IF(注文書!C11="","",注文書!C11)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
+      <c r="A11" s="18" t="str">
+        <f>IF(注文書!A12="","",注文書!A12)</f>
+        <v/>
+      </c>
+      <c r="B11" s="21" t="str">
+        <f>IF(注文書!B12="","",注文書!B12)</f>
+        <v/>
+      </c>
+      <c r="C11" s="25" t="str">
+        <f>IF(注文書!D12="","",注文書!D12)</f>
+        <v/>
+      </c>
+      <c r="D11" s="22" t="str">
+        <f>IF(注文書!C12="","",注文書!C12)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
+      <c r="A12" s="18" t="str">
+        <f>IF(注文書!A13="","",注文書!A13)</f>
+        <v/>
+      </c>
+      <c r="B12" s="21" t="str">
+        <f>IF(注文書!B13="","",注文書!B13)</f>
+        <v/>
+      </c>
+      <c r="C12" s="25" t="str">
+        <f>IF(注文書!D13="","",注文書!D13)</f>
+        <v/>
+      </c>
+      <c r="D12" s="22" t="str">
+        <f>IF(注文書!C13="","",注文書!C13)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
+      <c r="A13" s="18" t="str">
+        <f>IF(注文書!A14="","",注文書!A14)</f>
+        <v/>
+      </c>
+      <c r="B13" s="21" t="str">
+        <f>IF(注文書!B14="","",注文書!B14)</f>
+        <v/>
+      </c>
+      <c r="C13" s="25" t="str">
+        <f>IF(注文書!D14="","",注文書!D14)</f>
+        <v/>
+      </c>
+      <c r="D13" s="22" t="str">
+        <f>IF(注文書!C14="","",注文書!C14)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
+      <c r="A14" s="18" t="str">
+        <f>IF(注文書!A15="","",注文書!A15)</f>
+        <v/>
+      </c>
+      <c r="B14" s="21" t="str">
+        <f>IF(注文書!B15="","",注文書!B15)</f>
+        <v/>
+      </c>
+      <c r="C14" s="25" t="str">
+        <f>IF(注文書!D15="","",注文書!D15)</f>
+        <v/>
+      </c>
+      <c r="D14" s="22" t="str">
+        <f>IF(注文書!C15="","",注文書!C15)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
+      <c r="A15" s="18" t="str">
+        <f>IF(注文書!A16="","",注文書!A16)</f>
+        <v/>
+      </c>
+      <c r="B15" s="21" t="str">
+        <f>IF(注文書!B16="","",注文書!B16)</f>
+        <v/>
+      </c>
+      <c r="C15" s="25" t="str">
+        <f>IF(注文書!D16="","",注文書!D16)</f>
+        <v/>
+      </c>
+      <c r="D15" s="22" t="str">
+        <f>IF(注文書!C16="","",注文書!C16)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
+      <c r="A16" s="18" t="str">
+        <f>IF(注文書!A17="","",注文書!A17)</f>
+        <v/>
+      </c>
+      <c r="B16" s="21" t="str">
+        <f>IF(注文書!B17="","",注文書!B17)</f>
+        <v/>
+      </c>
+      <c r="C16" s="25" t="str">
+        <f>IF(注文書!D17="","",注文書!D17)</f>
+        <v/>
+      </c>
+      <c r="D16" s="22" t="str">
+        <f>IF(注文書!C17="","",注文書!C17)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
+      <c r="A17" s="18" t="str">
+        <f>IF(注文書!A18="","",注文書!A18)</f>
+        <v/>
+      </c>
+      <c r="B17" s="21" t="str">
+        <f>IF(注文書!B18="","",注文書!B18)</f>
+        <v/>
+      </c>
+      <c r="C17" s="25" t="str">
+        <f>IF(注文書!D18="","",注文書!D18)</f>
+        <v/>
+      </c>
+      <c r="D17" s="22" t="str">
+        <f>IF(注文書!C18="","",注文書!C18)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
+      <c r="A18" s="18" t="str">
+        <f>IF(注文書!A19="","",注文書!A19)</f>
+        <v/>
+      </c>
+      <c r="B18" s="21" t="str">
+        <f>IF(注文書!B19="","",注文書!B19)</f>
+        <v/>
+      </c>
+      <c r="C18" s="25" t="str">
+        <f>IF(注文書!D19="","",注文書!D19)</f>
+        <v/>
+      </c>
+      <c r="D18" s="22" t="str">
+        <f>IF(注文書!C19="","",注文書!C19)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="25"/>
+      <c r="A19" s="18" t="str">
+        <f>IF(注文書!A20="","",注文書!A20)</f>
+        <v/>
+      </c>
+      <c r="B19" s="21" t="str">
+        <f>IF(注文書!B20="","",注文書!B20)</f>
+        <v/>
+      </c>
+      <c r="C19" s="25" t="str">
+        <f>IF(注文書!D20="","",注文書!D20)</f>
+        <v/>
+      </c>
+      <c r="D19" s="22" t="str">
+        <f>IF(注文書!C20="","",注文書!C20)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="27"/>
+      <c r="A20" s="23" t="str">
+        <f>IF(注文書!A21="","",注文書!A21)</f>
+        <v/>
+      </c>
+      <c r="B20" s="24" t="str">
+        <f>IF(注文書!B21="","",注文書!B21)</f>
+        <v/>
+      </c>
+      <c r="C20" s="26" t="str">
+        <f>IF(注文書!D21="","",注文書!D21)</f>
+        <v/>
+      </c>
+      <c r="D20" s="24" t="str">
+        <f>IF(注文書!C21="","",注文書!C21)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="27"/>
+      <c r="A21" s="23" t="str">
+        <f>IF(注文書!A22="","",注文書!A22)</f>
+        <v/>
+      </c>
+      <c r="B21" s="24" t="str">
+        <f>IF(注文書!B22="","",注文書!B22)</f>
+        <v/>
+      </c>
+      <c r="C21" s="26" t="str">
+        <f>IF(注文書!D22="","",注文書!D22)</f>
+        <v/>
+      </c>
+      <c r="D21" s="24" t="str">
+        <f>IF(注文書!C22="","",注文書!C22)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="27"/>
-    </row>
-    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-    </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
+      <c r="A22" s="23" t="str">
+        <f>IF(注文書!A23="","",注文書!A23)</f>
+        <v/>
+      </c>
+      <c r="B22" s="24" t="str">
+        <f>IF(注文書!B23="","",注文書!B23)</f>
+        <v/>
+      </c>
+      <c r="C22" s="26" t="str">
+        <f>IF(注文書!D23="","",注文書!D23)</f>
+        <v/>
+      </c>
+      <c r="D22" s="24" t="str">
+        <f>IF(注文書!C23="","",注文書!C23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="34"/>
+    </row>
+    <row r="25" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="C3:D4"/>
+    <mergeCell ref="D24:D25"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+      <formula>ISNUMBER($B$1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="11" scale="82" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31093A61-3775-4FAC-9AC3-10FEA470F75D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" style="8" customWidth="1"/>
+    <col min="3" max="4" width="12.90625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10">
+        <f ca="1">TODAY()</f>
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+    </row>
+    <row r="4" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+    </row>
+    <row r="5" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="C5" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" spans="1:5" s="15" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="50"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="51"/>
+    </row>
+    <row r="9" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="50"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="51"/>
+    </row>
+    <row r="10" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="50"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="51"/>
+    </row>
+    <row r="11" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="50"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="51"/>
+    </row>
+    <row r="12" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="50"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="51"/>
+    </row>
+    <row r="13" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="50"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="51"/>
+    </row>
+    <row r="14" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="50"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="50"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="51"/>
+    </row>
+    <row r="16" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="50"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="51"/>
+    </row>
+    <row r="17" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="50"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="51"/>
+    </row>
+    <row r="18" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="50"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="51"/>
+    </row>
+    <row r="19" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="50"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="51"/>
+    </row>
+    <row r="20" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="50"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="51"/>
+    </row>
+    <row r="21" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="52"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="51"/>
+    </row>
+    <row r="22" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="52"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="51"/>
+    </row>
+    <row r="23" spans="1:5" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="53"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56"/>
+    </row>
+    <row r="24" spans="1:5" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="B1">
@@ -1419,51 +2419,33 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="11" scale="93" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="11" scale="97" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{62D317FC-23B3-4CB6-B9C5-8928CBC6AB6F}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{6AF9C3ED-0326-43D0-AC30-C7C1B7F2A73D}">
           <x14:formula1>
-            <xm:f>日付リスト!$A$2:$A$46</xm:f>
+            <xm:f>備考一覧!$A$2:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>A24</xm:sqref>
+          <xm:sqref>C8:C23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{CB6FF735-E05C-4C86-8E10-934425A236B5}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{8A39ED25-7715-41BF-A9C5-7A8F22D30002}">
           <x14:formula1>
-            <xm:f>商品名一覧!$A$2:$A$101</xm:f>
+            <xm:f>商品名一覧!$A$2:$A$53</xm:f>
           </x14:formula1>
-          <xm:sqref>B23:B24</xm:sqref>
+          <xm:sqref>B8:C23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{D67EA904-5FF8-4687-8A2C-124F5F44FD48}">
-          <x14:formula1>
-            <xm:f>OFFSET(日付リスト!$A$2,0,0,COUNT(日付リスト!$A$2:$A$46),1)</xm:f>
-          </x14:formula1>
-          <xm:sqref>A7:A22</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{01542218-C740-4094-ADE7-4A3A6884B42B}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{288C5C4D-FDB3-4DA2-AFF2-313CAF9EABB6}">
           <x14:formula1>
             <xm:f>日付リスト!$C$2:$C$14</xm:f>
           </x14:formula1>
           <xm:sqref>B1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{CE5A62FE-65B6-4044-A9B9-83750C803BE4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{336537E5-A39F-40F2-A987-6EC9B496D311}">
           <x14:formula1>
-            <xm:f>備考一覧!$A$2:$A$100</xm:f>
+            <xm:f>OFFSET(日付リスト!$A$2,0,0,COUNT(日付リスト!$A$2:$A$46),1)</xm:f>
           </x14:formula1>
-          <xm:sqref>C23:C24</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{13D6FBBB-F314-4BEC-B11B-EA8AB336D583}">
-          <x14:formula1>
-            <xm:f>商品名一覧!$A$2:$A$53</xm:f>
-          </x14:formula1>
-          <xm:sqref>B7:B22</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{F8012672-5D7E-49A8-A4B5-9FE9796B914C}">
-          <x14:formula1>
-            <xm:f>備考一覧!$A$2:$A$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>D7:D22</xm:sqref>
+          <xm:sqref>A8:A23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1471,7 +2453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -1482,279 +2464,279 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
@@ -1908,7 +2890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36E415E-C943-43E4-AE41-011A0B49F18B}">
   <dimension ref="A1:D100"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -1918,74 +2900,74 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -2259,54 +3241,54 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25046304-64E5-4F5F-B5FE-0FABAA79331A}">
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +3297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:C46"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -2326,16 +3308,16 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+0)=MONTH(注文書!$B$1),注文書!$B$1+0,""),TODAY()+0)</f>
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+1)=MONTH(注文書!$B$1),注文書!$B$1+1,""),TODAY()+1)</f>
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="6">
         <v>46174</v>
@@ -2344,7 +3326,7 @@
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+2)=MONTH(注文書!$B$1),注文書!$B$1+2,""),TODAY()+2)</f>
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="C4" s="6">
         <v>46204</v>
@@ -2353,7 +3335,7 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+3)=MONTH(注文書!$B$1),注文書!$B$1+3,""),TODAY()+3)</f>
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="C5" s="6">
         <v>46235</v>
@@ -2362,7 +3344,7 @@
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+4)=MONTH(注文書!$B$1),注文書!$B$1+4,""),TODAY()+4)</f>
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="C6" s="6">
         <v>46266</v>
@@ -2371,7 +3353,7 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+5)=MONTH(注文書!$B$1),注文書!$B$1+5,""),TODAY()+5)</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="C7" s="6">
         <v>46296</v>
@@ -2380,7 +3362,7 @@
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+6)=MONTH(注文書!$B$1),注文書!$B$1+6,""),TODAY()+6)</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="C8" s="6">
         <v>46327</v>
@@ -2389,7 +3371,7 @@
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+7)=MONTH(注文書!$B$1),注文書!$B$1+7,""),TODAY()+7)</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="C9" s="6">
         <v>46357</v>
@@ -2398,7 +3380,7 @@
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+8)=MONTH(注文書!$B$1),注文書!$B$1+8,""),TODAY()+8)</f>
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="C10" s="6">
         <v>46388</v>
@@ -2407,7 +3389,7 @@
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+9)=MONTH(注文書!$B$1),注文書!$B$1+9,""),TODAY()+9)</f>
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C11" s="6">
         <v>46419</v>
@@ -2416,7 +3398,7 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+10)=MONTH(注文書!$B$1),注文書!$B$1+10,""),TODAY()+10)</f>
-        <v>46220</v>
+        <v>46222</v>
       </c>
       <c r="C12" s="6">
         <v>46447</v>
@@ -2425,7 +3407,7 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+11)=MONTH(注文書!$B$1),注文書!$B$1+11,""),TODAY()+11)</f>
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C13" s="6">
         <v>46478</v>
@@ -2434,7 +3416,7 @@
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+12)=MONTH(注文書!$B$1),注文書!$B$1+12,""),TODAY()+12)</f>
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="C14" s="6">
         <v>46508</v>
@@ -2443,193 +3425,193 @@
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+13)=MONTH(注文書!$B$1),注文書!$B$1+13,""),TODAY()+13)</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+14)=MONTH(注文書!$B$1),注文書!$B$1+14,""),TODAY()+14)</f>
-        <v>46224</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+15)=MONTH(注文書!$B$1),注文書!$B$1+15,""),TODAY()+15)</f>
-        <v>46225</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+16)=MONTH(注文書!$B$1),注文書!$B$1+16,""),TODAY()+16)</f>
-        <v>46226</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+17)=MONTH(注文書!$B$1),注文書!$B$1+17,""),TODAY()+17)</f>
-        <v>46227</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+18)=MONTH(注文書!$B$1),注文書!$B$1+18,""),TODAY()+18)</f>
-        <v>46228</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+19)=MONTH(注文書!$B$1),注文書!$B$1+19,""),TODAY()+19)</f>
-        <v>46229</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+20)=MONTH(注文書!$B$1),注文書!$B$1+20,""),TODAY()+20)</f>
-        <v>46230</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+21)=MONTH(注文書!$B$1),注文書!$B$1+21,""),TODAY()+21)</f>
-        <v>46231</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+22)=MONTH(注文書!$B$1),注文書!$B$1+22,""),TODAY()+22)</f>
-        <v>46232</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+23)=MONTH(注文書!$B$1),注文書!$B$1+23,""),TODAY()+23)</f>
-        <v>46233</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+24)=MONTH(注文書!$B$1),注文書!$B$1+24,""),TODAY()+24)</f>
-        <v>46234</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+25)=MONTH(注文書!$B$1),注文書!$B$1+25,""),TODAY()+25)</f>
-        <v>46235</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+26)=MONTH(注文書!$B$1),注文書!$B$1+26,""),TODAY()+26)</f>
-        <v>46236</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+27)=MONTH(注文書!$B$1),注文書!$B$1+27,""),TODAY()+27)</f>
-        <v>46237</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+28)=MONTH(注文書!$B$1),注文書!$B$1+28,""),TODAY()+28)</f>
-        <v>46238</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+29)=MONTH(注文書!$B$1),注文書!$B$1+29,""),TODAY()+29)</f>
-        <v>46239</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+30)=MONTH(注文書!$B$1),注文書!$B$1+30,""),TODAY()+30)</f>
-        <v>46240</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+31)=MONTH(注文書!$B$1),注文書!$B$1+31,""),TODAY()+31)</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+32)=MONTH(注文書!$B$1),注文書!$B$1+32,""),TODAY()+32)</f>
-        <v>46242</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+33)=MONTH(注文書!$B$1),注文書!$B$1+33,""),TODAY()+33)</f>
-        <v>46243</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+34)=MONTH(注文書!$B$1),注文書!$B$1+34,""),TODAY()+34)</f>
-        <v>46244</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+35)=MONTH(注文書!$B$1),注文書!$B$1+35,""),TODAY()+35)</f>
-        <v>46245</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+36)=MONTH(注文書!$B$1),注文書!$B$1+36,""),TODAY()+36)</f>
-        <v>46246</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+37)=MONTH(注文書!$B$1),注文書!$B$1+37,""),TODAY()+37)</f>
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+38)=MONTH(注文書!$B$1),注文書!$B$1+38,""),TODAY()+38)</f>
-        <v>46248</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+39)=MONTH(注文書!$B$1),注文書!$B$1+39,""),TODAY()+39)</f>
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+40)=MONTH(注文書!$B$1),注文書!$B$1+40,""),TODAY()+40)</f>
-        <v>46250</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+41)=MONTH(注文書!$B$1),注文書!$B$1+41,""),TODAY()+41)</f>
-        <v>46251</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+42)=MONTH(注文書!$B$1),注文書!$B$1+42,""),TODAY()+42)</f>
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+43)=MONTH(注文書!$B$1),注文書!$B$1+43,""),TODAY()+43)</f>
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+44)=MONTH(注文書!$B$1),注文書!$B$1+44,""),TODAY()+44)</f>
-        <v>46254</v>
+        <v>46256</v>
       </c>
     </row>
   </sheetData>
